--- a/referral_form_templates/020_pediatrician_referral_form--referral_form_templates.xlsx
+++ b/referral_form_templates/020_pediatrician_referral_form--referral_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'asthma'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Asthma'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'adhd'}</t>
+          <t>adhd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'ADHD'}</t>
+          <t>ADHD</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'autism'}</t>
+          <t>autism</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Autism'}</t>
+          <t>Autism</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'cancer'}</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Cancer'}</t>
+          <t>Cancer</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'acetaminophen'}</t>
+          <t>acetaminophen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Acetaminophen'}</t>
+          <t>Acetaminophen</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'albuterol'}</t>
+          <t>albuterol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Albuterol'}</t>
+          <t>Albuterol</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'amoxicillin'}</t>
+          <t>amoxicillin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Amoxicillin'}</t>
+          <t>Amoxicillin</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'peanuts'}</t>
+          <t>peanuts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Peanuts'}</t>
+          <t>Peanuts</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'tree_nuts'}</t>
+          <t>tree_nuts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Tree Nuts'}</t>
+          <t>Tree Nuts</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Family Member'}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'general_practitioner'}</t>
+          <t>general_practitioner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'General Practitioner'}</t>
+          <t>General Practitioner</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'specialist'}</t>
+          <t>specialist</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Specialist'}</t>
+          <t>Specialist</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'nurse'}</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Nurse'}</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
